--- a/basedatos_partidas/salida/descompuestos/07.05.02.040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.05.02.040.xlsx
@@ -584,10 +584,10 @@
         <v>0.2</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>61.36</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="14">
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>67.84</v>
+        <v>67.88</v>
       </c>
       <c r="H23" t="n">
         <v>0.68</v>
@@ -814,7 +814,7 @@
       </c>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="5" t="n">
-        <v>68.52</v>
+        <v>68.56</v>
       </c>
     </row>
   </sheetData>
